--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260902.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260902.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>14.98%</t>
+          <t>14.86%</t>
         </is>
       </c>
     </row>
@@ -638,51 +638,51 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>12.86%</t>
+          <t>12.66%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>179,740,000</t>
+          <t>915,097,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>10.38%</t>
+          <t>10.32%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>915,097,000</t>
+          <t>179,740,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>10.28%</t>
+          <t>10.26%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>8.40%</t>
+          <t>8.61%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>6.29%</t>
+          <t>6.30%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.03%</t>
+          <t>5.12%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>3.94%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.38%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>129,090,000</t>
+          <t>130,610,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>202609TX</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>台指期</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>93,280,000</t>
+          <t>556</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>202609TX</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>台指期</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>94,560,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>119,660,000</t>
+          <t>77,000,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,22 +1107,22 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>77,000,000</t>
+          <t>119,660,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>36,840,000</t>
+          <t>27,972,899</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>27,972,899</t>
+          <t>30,838,800</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>30,838,800</t>
+          <t>36,840,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>15,520,000</t>
+          <t>41,500,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,22 +1437,22 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>41,500,000</t>
+          <t>15,520,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>5,268,906,020</t>
+          <t>5,805,595,968</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,313,627,312</t>
+          <t>1,213,378,752</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>-2,270,026,781</t>
+          <t>-2,087,730,947</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr"/>
